--- a/ig/ch-vacd/StructureDefinition-ch-vacd-recommendation-request-messageheader.xlsx
+++ b/ig/ch-vacd/StructureDefinition-ch-vacd-recommendation-request-messageheader.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T10:03:10+00:00</t>
+    <t>2026-06-11T13:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1008,7 +1008,7 @@
     <t>MessageHeader.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://fhir.ch/ig/ch-core/StructureDefinition/ch-core-patient-epr|http://fhir.ch/ig/ch-core/StructureDefinition/ch-core-practitionerrole|http://fhir.ch/ig/ch-core/StructureDefinition/ch-core-practitioner|http://fhir.ch/ig/ch-core/StructureDefinition/ch-core-organization|http://fhir.ch/ig/ch-vacd/StructureDefinition/ch-vacd-allergyintolerances|http://fhir.ch/ig/ch-vacd/StructureDefinition/ch-vacd-immunization|http://fhir.ch/ig/ch-vacd/StructureDefinition/ch-vacd-laboratory-serology|http://fhir.ch/ig/ch-vacd/StructureDefinition/ch-vacd-medical-problems|http://fhir.ch/ig/ch-vacd/StructureDefinition/ch-vacd-pastillnesses|http://fhir.ch/ig/ch-vacd/StructureDefinition/ch-vacd-basic-immunization|Consent)
+    <t xml:space="preserve">Reference(http://fhir.ch/ig/ch-core/StructureDefinition/ch-core-patient-epr|http://fhir.ch/ig/ch-core/StructureDefinition/ch-core-practitionerrole|http://fhir.ch/ig/ch-core/StructureDefinition/ch-core-practitioner|http://fhir.ch/ig/ch-core/StructureDefinition/ch-core-organization|http://fhir.ch/ig/ch-vacd/StructureDefinition/ch-vacd-allergyintolerances|http://fhir.ch/ig/ch-vacd/StructureDefinition/ch-vacd-immunization|http://fhir.ch/ig/ch-vacd/StructureDefinition/ch-vacd-laboratory-serology|http://fhir.ch/ig/ch-vacd/StructureDefinition/ch-vacd-medical-problems|http://fhir.ch/ig/ch-vacd/StructureDefinition/ch-vacd-pastillnesses|http://fhir.ch/ig/ch-vacd/StructureDefinition/ch-vacd-basic-immunization|http://fhir.ch/ig/ch-vacd/StructureDefinition/ch-vacd-travel-information|Consent)
 </t>
   </si>
   <si>
